--- a/data.mn/public/datasets/mongolbank-bank-balance-sheet.xlsx
+++ b/data.mn/public/datasets/mongolbank-bank-balance-sheet.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,9 +418,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -430,17 +431,4395 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>total_assets_billion_mnt</t>
+          <t>Capital</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>total_liabilities_billion_mnt</t>
+          <t>Total Assets</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>capital_billion_mnt</t>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>114.169</v>
+      </c>
+      <c r="C2" t="n">
+        <v>825.095</v>
+      </c>
+      <c r="D2" t="n">
+        <v>710.926</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2004-02-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>121.656</v>
+      </c>
+      <c r="C3" t="n">
+        <v>876.437</v>
+      </c>
+      <c r="D3" t="n">
+        <v>754.7809999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2004-03-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>138.016</v>
+      </c>
+      <c r="C4" t="n">
+        <v>912.824</v>
+      </c>
+      <c r="D4" t="n">
+        <v>774.808</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2004-04-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>138.425</v>
+      </c>
+      <c r="C5" t="n">
+        <v>931.888</v>
+      </c>
+      <c r="D5" t="n">
+        <v>793.463</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2004-05-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>139.24</v>
+      </c>
+      <c r="C6" t="n">
+        <v>974.943</v>
+      </c>
+      <c r="D6" t="n">
+        <v>835.703</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2004-06-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>141.027</v>
+      </c>
+      <c r="C7" t="n">
+        <v>977.532</v>
+      </c>
+      <c r="D7" t="n">
+        <v>836.505</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2004-07-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>145.17</v>
+      </c>
+      <c r="C8" t="n">
+        <v>995.125</v>
+      </c>
+      <c r="D8" t="n">
+        <v>849.955</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2004-08-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>147.483</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1040.788</v>
+      </c>
+      <c r="D9" t="n">
+        <v>893.306</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>146.739</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1031.215</v>
+      </c>
+      <c r="D10" t="n">
+        <v>884.476</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>147.079</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1053.49</v>
+      </c>
+      <c r="D11" t="n">
+        <v>906.4109999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>153.309</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1092.658</v>
+      </c>
+      <c r="D12" t="n">
+        <v>939.35</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>167.101</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1108.846</v>
+      </c>
+      <c r="D13" t="n">
+        <v>941.745</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>169.996</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1121.305</v>
+      </c>
+      <c r="D14" t="n">
+        <v>951.309</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2005-02-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>168.282</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1139.124</v>
+      </c>
+      <c r="D15" t="n">
+        <v>970.843</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2005-03-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>170.958</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1164.294</v>
+      </c>
+      <c r="D16" t="n">
+        <v>993.336</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2005-04-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>175.455</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1199.425</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1023.97</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2005-05-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>176.843</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1233.997</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1057.154</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2005-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>179.449</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1292.06</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1112.611</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2005-07-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>182.628</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1309.585</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1126.957</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2005-08-01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>187.729</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1364.29</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1176.561</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2005-09-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>190.709</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1416.654</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1225.945</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2005-10-01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>194.423</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1434.186</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1239.764</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2005-11-01</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>200.994</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1503.233</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1302.239</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2005-12-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>207.076</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1585.037</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1377.962</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>209.39</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1587.994</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1378.604</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2006-02-01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>212.597</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1614.047</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1401.45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2006-03-01</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>226.021</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1671.673</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1445.652</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2006-04-01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>236.114</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2037.047</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1800.933</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2006-05-01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>240.426</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2096.267</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1855.841</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2006-06-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>242.355</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2010.974</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1768.619</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2006-07-01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>248.925</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2206.583</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1957.657</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2006-08-01</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>254.988</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2121.644</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1866.657</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2006-09-01</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>264.231</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2248.815</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1984.583</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2006-10-01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>270.288</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2246.663</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1976.375</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2006-11-01</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>275.244</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2243.992</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1968.748</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2006-12-01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>294.78</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2314.598</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2019.818</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>291.78</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2272.621</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1980.841</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2007-02-01</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>294.162</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2366.97</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2072.808</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2007-03-01</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>301.47</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2480.975</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2179.505</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2007-04-01</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>307.336</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2629.118</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2321.782</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2007-05-01</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>311.119</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2680.439</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2369.319</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2007-06-01</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>318.872</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2771.14</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2452.268</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>326.816</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2834.201</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2507.385</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2007-08-01</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>335.074</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2954.615</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2619.541</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2007-09-01</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>345.391</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3009.815</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2664.424</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2007-10-01</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>354.67</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3134.817</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2780.147</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2007-11-01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>365.735</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3139.876</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2774.141</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2007-12-01</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>376.386</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3383.952</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3007.566</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>383.491</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3295.108</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2911.618</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2008-02-01</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>391.568</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3445.096</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3053.529</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2008-03-01</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>404.061</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3573.296</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3169.235</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2008-04-01</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>412.169</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3683.613</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3271.444</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2008-05-01</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>419.97</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3774.841</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3354.871</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2008-06-01</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>426.621</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3849.377</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3422.756</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2008-07-01</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>444.801</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3929.563</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3484.762</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2008-08-01</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>448.807</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3924.941</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3476.135</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2008-09-01</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>479.801</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3961.662</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3481.86</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2008-10-01</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>485.38</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3856.916</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3371.536</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2008-11-01</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>492.639</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3837.667</v>
+      </c>
+      <c r="D60" t="n">
+        <v>3345.028</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2008-12-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>436.823</v>
+      </c>
+      <c r="C61" t="n">
+        <v>3519.427</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3082.604</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>445.67</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3568.791</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3123.121</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2009-02-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>450.783</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3721.86</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3271.077</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2009-03-01</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>456.74</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3761.312</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3304.572</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2009-04-01</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>422.733</v>
+      </c>
+      <c r="C65" t="n">
+        <v>3370.877</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2948.143</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2009-05-01</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>402.416</v>
+      </c>
+      <c r="C66" t="n">
+        <v>3375.101</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2972.685</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2009-06-01</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>409.995</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3504.924</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3094.929</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2009-07-01</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>376.002</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3559.089</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3183.087</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>390.261</v>
+      </c>
+      <c r="C69" t="n">
+        <v>3624.029</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3233.768</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>411.609</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3712.612</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3301.004</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>410.381</v>
+      </c>
+      <c r="C71" t="n">
+        <v>3784.507</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3374.126</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>420.252</v>
+      </c>
+      <c r="C72" t="n">
+        <v>4148.475</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3728.224</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>460.66</v>
+      </c>
+      <c r="C73" t="n">
+        <v>4290.574</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3829.913</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>472.201</v>
+      </c>
+      <c r="C74" t="n">
+        <v>4225.582</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3753.383</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2010-02-01</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>495.548</v>
+      </c>
+      <c r="C75" t="n">
+        <v>4377.334</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3881.786</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2010-03-01</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>496.649</v>
+      </c>
+      <c r="C76" t="n">
+        <v>4395.993</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3899.345</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>497.018</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4518.79</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4021.772</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2010-05-01</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>500.814</v>
+      </c>
+      <c r="C78" t="n">
+        <v>4596.529</v>
+      </c>
+      <c r="D78" t="n">
+        <v>4095.716</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2010-06-01</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>532.953</v>
+      </c>
+      <c r="C79" t="n">
+        <v>4868.726</v>
+      </c>
+      <c r="D79" t="n">
+        <v>4335.773</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2010-07-01</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>529.718</v>
+      </c>
+      <c r="C80" t="n">
+        <v>4873.565</v>
+      </c>
+      <c r="D80" t="n">
+        <v>4343.847</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2010-08-01</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>535.226</v>
+      </c>
+      <c r="C81" t="n">
+        <v>4966.261</v>
+      </c>
+      <c r="D81" t="n">
+        <v>4431.035</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2010-09-01</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>541.364</v>
+      </c>
+      <c r="C82" t="n">
+        <v>5210.491</v>
+      </c>
+      <c r="D82" t="n">
+        <v>4669.128</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2010-10-01</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>561.668</v>
+      </c>
+      <c r="C83" t="n">
+        <v>5492.19</v>
+      </c>
+      <c r="D83" t="n">
+        <v>4930.523</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2010-11-01</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>607.898</v>
+      </c>
+      <c r="C84" t="n">
+        <v>5542.216</v>
+      </c>
+      <c r="D84" t="n">
+        <v>4934.318</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2010-12-01</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>618.068</v>
+      </c>
+      <c r="C85" t="n">
+        <v>6219.488</v>
+      </c>
+      <c r="D85" t="n">
+        <v>5601.42</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>629.855</v>
+      </c>
+      <c r="C86" t="n">
+        <v>6384.313</v>
+      </c>
+      <c r="D86" t="n">
+        <v>5754.458</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>634.4059999999999</v>
+      </c>
+      <c r="C87" t="n">
+        <v>6557.719</v>
+      </c>
+      <c r="D87" t="n">
+        <v>5923.312</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2011-03-01</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>656.175</v>
+      </c>
+      <c r="C88" t="n">
+        <v>6666.919</v>
+      </c>
+      <c r="D88" t="n">
+        <v>6010.744</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2011-04-01</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>660.4589999999999</v>
+      </c>
+      <c r="C89" t="n">
+        <v>6910.622</v>
+      </c>
+      <c r="D89" t="n">
+        <v>6250.163</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2011-05-01</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>684.953</v>
+      </c>
+      <c r="C90" t="n">
+        <v>7193.967</v>
+      </c>
+      <c r="D90" t="n">
+        <v>6509.014</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2011-06-01</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>747.952</v>
+      </c>
+      <c r="C91" t="n">
+        <v>7683.802</v>
+      </c>
+      <c r="D91" t="n">
+        <v>6935.851</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2011-07-01</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>751.823</v>
+      </c>
+      <c r="C92" t="n">
+        <v>7862.015</v>
+      </c>
+      <c r="D92" t="n">
+        <v>7110.202</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2011-08-01</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>773.5599999999999</v>
+      </c>
+      <c r="C93" t="n">
+        <v>7808.674</v>
+      </c>
+      <c r="D93" t="n">
+        <v>7035.199</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2011-09-01</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>805.768</v>
+      </c>
+      <c r="C94" t="n">
+        <v>8186.386</v>
+      </c>
+      <c r="D94" t="n">
+        <v>7380.618</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2011-10-01</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>822.211</v>
+      </c>
+      <c r="C95" t="n">
+        <v>8313.464</v>
+      </c>
+      <c r="D95" t="n">
+        <v>7491.252</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2011-11-01</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>867.505</v>
+      </c>
+      <c r="C96" t="n">
+        <v>8444.746999999999</v>
+      </c>
+      <c r="D96" t="n">
+        <v>7577.242</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2011-12-01</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>913.489</v>
+      </c>
+      <c r="C97" t="n">
+        <v>9362.245000000001</v>
+      </c>
+      <c r="D97" t="n">
+        <v>8448.758</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2012-01-01</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>933.785</v>
+      </c>
+      <c r="C98" t="n">
+        <v>8797.633</v>
+      </c>
+      <c r="D98" t="n">
+        <v>7863.847</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2012-02-01</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>945.0890000000001</v>
+      </c>
+      <c r="C99" t="n">
+        <v>8920.539000000001</v>
+      </c>
+      <c r="D99" t="n">
+        <v>7975.449</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2012-03-01</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>976.6849999999999</v>
+      </c>
+      <c r="C100" t="n">
+        <v>9349.089</v>
+      </c>
+      <c r="D100" t="n">
+        <v>8372.404</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2012-04-01</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1003.434</v>
+      </c>
+      <c r="C101" t="n">
+        <v>9397.984</v>
+      </c>
+      <c r="D101" t="n">
+        <v>8394.549000000001</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2012-05-01</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1018.203</v>
+      </c>
+      <c r="C102" t="n">
+        <v>9720.128000000001</v>
+      </c>
+      <c r="D102" t="n">
+        <v>8701.925999999999</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2012-06-01</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1084.034</v>
+      </c>
+      <c r="C103" t="n">
+        <v>10336.851</v>
+      </c>
+      <c r="D103" t="n">
+        <v>9252.816000000001</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2012-07-01</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1099.574</v>
+      </c>
+      <c r="C104" t="n">
+        <v>10140.701</v>
+      </c>
+      <c r="D104" t="n">
+        <v>9041.127</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2012-08-01</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1117.331</v>
+      </c>
+      <c r="C105" t="n">
+        <v>10296.373</v>
+      </c>
+      <c r="D105" t="n">
+        <v>9179.041999999999</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2012-09-01</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1143.496</v>
+      </c>
+      <c r="C106" t="n">
+        <v>10956.011</v>
+      </c>
+      <c r="D106" t="n">
+        <v>9812.513999999999</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2012-10-01</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1159.574</v>
+      </c>
+      <c r="C107" t="n">
+        <v>10913.905</v>
+      </c>
+      <c r="D107" t="n">
+        <v>9754.331</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2012-11-01</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1197.395</v>
+      </c>
+      <c r="C108" t="n">
+        <v>10909.363</v>
+      </c>
+      <c r="D108" t="n">
+        <v>9711.968000000001</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2012-12-01</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1223.789</v>
+      </c>
+      <c r="C109" t="n">
+        <v>11978.467</v>
+      </c>
+      <c r="D109" t="n">
+        <v>10754.678</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1289.62</v>
+      </c>
+      <c r="C110" t="n">
+        <v>12203.222</v>
+      </c>
+      <c r="D110" t="n">
+        <v>10913.602</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1257.928</v>
+      </c>
+      <c r="C111" t="n">
+        <v>12548.311</v>
+      </c>
+      <c r="D111" t="n">
+        <v>11290.383</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2013-03-01</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1266.623</v>
+      </c>
+      <c r="C112" t="n">
+        <v>13273.291</v>
+      </c>
+      <c r="D112" t="n">
+        <v>12006.669</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2013-04-01</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1294.035</v>
+      </c>
+      <c r="C113" t="n">
+        <v>13318.672</v>
+      </c>
+      <c r="D113" t="n">
+        <v>12024.635</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2013-05-01</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1317.922</v>
+      </c>
+      <c r="C114" t="n">
+        <v>14647.026</v>
+      </c>
+      <c r="D114" t="n">
+        <v>13329.104</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1383.886</v>
+      </c>
+      <c r="C115" t="n">
+        <v>15926.172</v>
+      </c>
+      <c r="D115" t="n">
+        <v>14542.285</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2013-07-01</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1364.714</v>
+      </c>
+      <c r="C116" t="n">
+        <v>16047.137</v>
+      </c>
+      <c r="D116" t="n">
+        <v>14682.423</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1425.157</v>
+      </c>
+      <c r="C117" t="n">
+        <v>16894.332</v>
+      </c>
+      <c r="D117" t="n">
+        <v>15469.176</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1544.752</v>
+      </c>
+      <c r="C118" t="n">
+        <v>18114.625</v>
+      </c>
+      <c r="D118" t="n">
+        <v>16569.873</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2013-10-01</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1576.65</v>
+      </c>
+      <c r="C119" t="n">
+        <v>18596.397</v>
+      </c>
+      <c r="D119" t="n">
+        <v>17019.747</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2013-11-01</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1588.817</v>
+      </c>
+      <c r="C120" t="n">
+        <v>19442.091</v>
+      </c>
+      <c r="D120" t="n">
+        <v>17853.274</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2013-12-01</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1718.711</v>
+      </c>
+      <c r="C121" t="n">
+        <v>20850.384</v>
+      </c>
+      <c r="D121" t="n">
+        <v>19131.689</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1753.628</v>
+      </c>
+      <c r="C122" t="n">
+        <v>19990.244</v>
+      </c>
+      <c r="D122" t="n">
+        <v>18236.616</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2014-02-01</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1775.296</v>
+      </c>
+      <c r="C123" t="n">
+        <v>20553.516</v>
+      </c>
+      <c r="D123" t="n">
+        <v>18778.22</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2014-03-01</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1876.367</v>
+      </c>
+      <c r="C124" t="n">
+        <v>20678.301</v>
+      </c>
+      <c r="D124" t="n">
+        <v>18801.934</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1941.828</v>
+      </c>
+      <c r="C125" t="n">
+        <v>21184.814</v>
+      </c>
+      <c r="D125" t="n">
+        <v>19242.986</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2014-05-01</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1959.847</v>
+      </c>
+      <c r="C126" t="n">
+        <v>21127.514</v>
+      </c>
+      <c r="D126" t="n">
+        <v>19167.666</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1998.354</v>
+      </c>
+      <c r="C127" t="n">
+        <v>21389.922</v>
+      </c>
+      <c r="D127" t="n">
+        <v>19391.567</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>2062.973</v>
+      </c>
+      <c r="C128" t="n">
+        <v>20948.194</v>
+      </c>
+      <c r="D128" t="n">
+        <v>18885.32</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>2060.504</v>
+      </c>
+      <c r="C129" t="n">
+        <v>20730.908</v>
+      </c>
+      <c r="D129" t="n">
+        <v>18670.404</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>2107.028</v>
+      </c>
+      <c r="C130" t="n">
+        <v>20916.562</v>
+      </c>
+      <c r="D130" t="n">
+        <v>18809.534</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2014-10-01</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2115.541</v>
+      </c>
+      <c r="C131" t="n">
+        <v>20955.894</v>
+      </c>
+      <c r="D131" t="n">
+        <v>18840.352</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2130.92</v>
+      </c>
+      <c r="C132" t="n">
+        <v>20583.187</v>
+      </c>
+      <c r="D132" t="n">
+        <v>18452.267</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2014-12-01</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>2335.949</v>
+      </c>
+      <c r="C133" t="n">
+        <v>22562.602</v>
+      </c>
+      <c r="D133" t="n">
+        <v>20226.652</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2353.272</v>
+      </c>
+      <c r="C134" t="n">
+        <v>20603.001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>18249.73</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2015-02-01</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>2394.708</v>
+      </c>
+      <c r="C135" t="n">
+        <v>20720.951</v>
+      </c>
+      <c r="D135" t="n">
+        <v>18326.243</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2015-03-01</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>2385.49</v>
+      </c>
+      <c r="C136" t="n">
+        <v>20759.734</v>
+      </c>
+      <c r="D136" t="n">
+        <v>18374.243</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2428.647</v>
+      </c>
+      <c r="C137" t="n">
+        <v>20480.179</v>
+      </c>
+      <c r="D137" t="n">
+        <v>18051.532</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2015-05-01</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>2507.369</v>
+      </c>
+      <c r="C138" t="n">
+        <v>21446.055</v>
+      </c>
+      <c r="D138" t="n">
+        <v>18938.686</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2015-06-01</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2497.475</v>
+      </c>
+      <c r="C139" t="n">
+        <v>21846.12</v>
+      </c>
+      <c r="D139" t="n">
+        <v>19348.645</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2015-07-01</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>2519.316</v>
+      </c>
+      <c r="C140" t="n">
+        <v>21443.828</v>
+      </c>
+      <c r="D140" t="n">
+        <v>18924.511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2015-08-01</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2476.24</v>
+      </c>
+      <c r="C141" t="n">
+        <v>21581.778</v>
+      </c>
+      <c r="D141" t="n">
+        <v>19105.538</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2015-09-01</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2550.507</v>
+      </c>
+      <c r="C142" t="n">
+        <v>21300.695</v>
+      </c>
+      <c r="D142" t="n">
+        <v>18750.188</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2015-10-01</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2580.765</v>
+      </c>
+      <c r="C143" t="n">
+        <v>20721.033</v>
+      </c>
+      <c r="D143" t="n">
+        <v>18140.268</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2015-11-01</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>2551.443</v>
+      </c>
+      <c r="C144" t="n">
+        <v>20696.271</v>
+      </c>
+      <c r="D144" t="n">
+        <v>18144.827</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2015-12-01</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>2603.013</v>
+      </c>
+      <c r="C145" t="n">
+        <v>21506.524</v>
+      </c>
+      <c r="D145" t="n">
+        <v>18903.512</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>2503.051</v>
+      </c>
+      <c r="C146" t="n">
+        <v>20843.475</v>
+      </c>
+      <c r="D146" t="n">
+        <v>18340.425</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2016-02-01</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>2511.349</v>
+      </c>
+      <c r="C147" t="n">
+        <v>21830.237</v>
+      </c>
+      <c r="D147" t="n">
+        <v>19318.887</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2016-03-01</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>2571.179</v>
+      </c>
+      <c r="C148" t="n">
+        <v>22028.087</v>
+      </c>
+      <c r="D148" t="n">
+        <v>19456.908</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2016-04-01</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2610.839</v>
+      </c>
+      <c r="C149" t="n">
+        <v>22215.488</v>
+      </c>
+      <c r="D149" t="n">
+        <v>19604.649</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2016-05-01</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>2622.437</v>
+      </c>
+      <c r="C150" t="n">
+        <v>22210.273</v>
+      </c>
+      <c r="D150" t="n">
+        <v>19587.836</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2016-06-01</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>2748.073</v>
+      </c>
+      <c r="C151" t="n">
+        <v>23297.189</v>
+      </c>
+      <c r="D151" t="n">
+        <v>20549.116</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2016-07-01</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>2816.476</v>
+      </c>
+      <c r="C152" t="n">
+        <v>23944.237</v>
+      </c>
+      <c r="D152" t="n">
+        <v>21127.761</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2016-08-01</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2851.603</v>
+      </c>
+      <c r="C153" t="n">
+        <v>24203.833</v>
+      </c>
+      <c r="D153" t="n">
+        <v>21352.229</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>2947.049</v>
+      </c>
+      <c r="C154" t="n">
+        <v>24642.082</v>
+      </c>
+      <c r="D154" t="n">
+        <v>21695.033</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>2972.739</v>
+      </c>
+      <c r="C155" t="n">
+        <v>24710.323</v>
+      </c>
+      <c r="D155" t="n">
+        <v>21737.584</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>2994.872</v>
+      </c>
+      <c r="C156" t="n">
+        <v>25035.525</v>
+      </c>
+      <c r="D156" t="n">
+        <v>22040.654</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2016-12-01</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>3113.367</v>
+      </c>
+      <c r="C157" t="n">
+        <v>25323.815</v>
+      </c>
+      <c r="D157" t="n">
+        <v>22210.447</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>3204.418</v>
+      </c>
+      <c r="C158" t="n">
+        <v>24912.657</v>
+      </c>
+      <c r="D158" t="n">
+        <v>21708.238</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2017-02-01</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>3286.957</v>
+      </c>
+      <c r="C159" t="n">
+        <v>25136.088</v>
+      </c>
+      <c r="D159" t="n">
+        <v>21849.13</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2017-03-01</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>3266.282</v>
+      </c>
+      <c r="C160" t="n">
+        <v>25159.241</v>
+      </c>
+      <c r="D160" t="n">
+        <v>21892.959</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>3267.446</v>
+      </c>
+      <c r="C161" t="n">
+        <v>25185.488</v>
+      </c>
+      <c r="D161" t="n">
+        <v>21918.042</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2017-05-01</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>3304.01</v>
+      </c>
+      <c r="C162" t="n">
+        <v>25691.944</v>
+      </c>
+      <c r="D162" t="n">
+        <v>22387.934</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2017-06-01</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>3233.443</v>
+      </c>
+      <c r="C163" t="n">
+        <v>25765.186</v>
+      </c>
+      <c r="D163" t="n">
+        <v>22531.743</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2017-07-01</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>3265.95</v>
+      </c>
+      <c r="C164" t="n">
+        <v>26683.532</v>
+      </c>
+      <c r="D164" t="n">
+        <v>23417.582</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>3240.225</v>
+      </c>
+      <c r="C165" t="n">
+        <v>27480.34</v>
+      </c>
+      <c r="D165" t="n">
+        <v>24240.115</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>3305.868</v>
+      </c>
+      <c r="C166" t="n">
+        <v>28062.556</v>
+      </c>
+      <c r="D166" t="n">
+        <v>24756.688</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2017-10-01</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>3348.175</v>
+      </c>
+      <c r="C167" t="n">
+        <v>27761.506</v>
+      </c>
+      <c r="D167" t="n">
+        <v>24413.331</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2017-11-01</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>3348.907</v>
+      </c>
+      <c r="C168" t="n">
+        <v>27651.383</v>
+      </c>
+      <c r="D168" t="n">
+        <v>24302.476</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2017-12-01</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>3330.618</v>
+      </c>
+      <c r="C169" t="n">
+        <v>28769.815</v>
+      </c>
+      <c r="D169" t="n">
+        <v>25439.197</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>3346.276</v>
+      </c>
+      <c r="C170" t="n">
+        <v>28027.452</v>
+      </c>
+      <c r="D170" t="n">
+        <v>24681.176</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2018-02-01</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>3358.243</v>
+      </c>
+      <c r="C171" t="n">
+        <v>28551.309</v>
+      </c>
+      <c r="D171" t="n">
+        <v>25193.067</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2018-03-01</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>3345.744</v>
+      </c>
+      <c r="C172" t="n">
+        <v>28931.117</v>
+      </c>
+      <c r="D172" t="n">
+        <v>25585.373</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>3405.117</v>
+      </c>
+      <c r="C173" t="n">
+        <v>28878.745</v>
+      </c>
+      <c r="D173" t="n">
+        <v>25473.628</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2018-05-01</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>3447.844</v>
+      </c>
+      <c r="C174" t="n">
+        <v>29820.264</v>
+      </c>
+      <c r="D174" t="n">
+        <v>26372.42</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>3361.452</v>
+      </c>
+      <c r="C175" t="n">
+        <v>30255.796</v>
+      </c>
+      <c r="D175" t="n">
+        <v>26894.344</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>3333.264</v>
+      </c>
+      <c r="C176" t="n">
+        <v>30035.633</v>
+      </c>
+      <c r="D176" t="n">
+        <v>26702.369</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>3228.093</v>
+      </c>
+      <c r="C177" t="n">
+        <v>30178.075</v>
+      </c>
+      <c r="D177" t="n">
+        <v>26949.982</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>3279.079</v>
+      </c>
+      <c r="C178" t="n">
+        <v>31030.494</v>
+      </c>
+      <c r="D178" t="n">
+        <v>27751.415</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>2988.741</v>
+      </c>
+      <c r="C179" t="n">
+        <v>31150.913</v>
+      </c>
+      <c r="D179" t="n">
+        <v>28162.171</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2018-11-01</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>3001.494</v>
+      </c>
+      <c r="C180" t="n">
+        <v>31912.239</v>
+      </c>
+      <c r="D180" t="n">
+        <v>28910.746</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2018-12-01</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>3427.54</v>
+      </c>
+      <c r="C181" t="n">
+        <v>33049.756</v>
+      </c>
+      <c r="D181" t="n">
+        <v>29622.216</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>3478.911</v>
+      </c>
+      <c r="C182" t="n">
+        <v>32687.102</v>
+      </c>
+      <c r="D182" t="n">
+        <v>29208.191</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2019-02-01</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>3486.062</v>
+      </c>
+      <c r="C183" t="n">
+        <v>32761.712</v>
+      </c>
+      <c r="D183" t="n">
+        <v>29275.65</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>3516.621</v>
+      </c>
+      <c r="C184" t="n">
+        <v>33512.61</v>
+      </c>
+      <c r="D184" t="n">
+        <v>29995.989</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>3696.269</v>
+      </c>
+      <c r="C185" t="n">
+        <v>33502.7</v>
+      </c>
+      <c r="D185" t="n">
+        <v>29806.43</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>3747.21</v>
+      </c>
+      <c r="C186" t="n">
+        <v>33742.979</v>
+      </c>
+      <c r="D186" t="n">
+        <v>29995.768</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>3770.968</v>
+      </c>
+      <c r="C187" t="n">
+        <v>34577.607</v>
+      </c>
+      <c r="D187" t="n">
+        <v>30806.639</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>3786.471</v>
+      </c>
+      <c r="C188" t="n">
+        <v>34122.266</v>
+      </c>
+      <c r="D188" t="n">
+        <v>30335.795</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>3765.462</v>
+      </c>
+      <c r="C189" t="n">
+        <v>34519.93</v>
+      </c>
+      <c r="D189" t="n">
+        <v>30754.468</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>3794.875</v>
+      </c>
+      <c r="C190" t="n">
+        <v>34827.392</v>
+      </c>
+      <c r="D190" t="n">
+        <v>31032.517</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>3716.936</v>
+      </c>
+      <c r="C191" t="n">
+        <v>34819.298</v>
+      </c>
+      <c r="D191" t="n">
+        <v>31102.362</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>3723.491</v>
+      </c>
+      <c r="C192" t="n">
+        <v>34792.688</v>
+      </c>
+      <c r="D192" t="n">
+        <v>31069.197</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>3697.235</v>
+      </c>
+      <c r="C193" t="n">
+        <v>35718.271</v>
+      </c>
+      <c r="D193" t="n">
+        <v>32021.036</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>3715.538</v>
+      </c>
+      <c r="C194" t="n">
+        <v>35080.846</v>
+      </c>
+      <c r="D194" t="n">
+        <v>31365.309</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2020-02-01</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>3710.579</v>
+      </c>
+      <c r="C195" t="n">
+        <v>35007.582</v>
+      </c>
+      <c r="D195" t="n">
+        <v>31297.002</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>3643.887</v>
+      </c>
+      <c r="C196" t="n">
+        <v>34853.715</v>
+      </c>
+      <c r="D196" t="n">
+        <v>31209.828</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>3624.646</v>
+      </c>
+      <c r="C197" t="n">
+        <v>34573.438</v>
+      </c>
+      <c r="D197" t="n">
+        <v>30948.792</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2020-05-01</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>3670.345</v>
+      </c>
+      <c r="C198" t="n">
+        <v>33276.848</v>
+      </c>
+      <c r="D198" t="n">
+        <v>29606.504</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>3748.594</v>
+      </c>
+      <c r="C199" t="n">
+        <v>34203.081</v>
+      </c>
+      <c r="D199" t="n">
+        <v>30454.487</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>3780.082</v>
+      </c>
+      <c r="C200" t="n">
+        <v>34315.574</v>
+      </c>
+      <c r="D200" t="n">
+        <v>30535.492</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2020-08-01</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>3788.834</v>
+      </c>
+      <c r="C201" t="n">
+        <v>34384.31</v>
+      </c>
+      <c r="D201" t="n">
+        <v>30595.476</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>3679.284</v>
+      </c>
+      <c r="C202" t="n">
+        <v>35262.79</v>
+      </c>
+      <c r="D202" t="n">
+        <v>31583.506</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>3682.463</v>
+      </c>
+      <c r="C203" t="n">
+        <v>34920.345</v>
+      </c>
+      <c r="D203" t="n">
+        <v>31237.882</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>3745.258</v>
+      </c>
+      <c r="C204" t="n">
+        <v>35810.451</v>
+      </c>
+      <c r="D204" t="n">
+        <v>32065.193</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>3749.402</v>
+      </c>
+      <c r="C205" t="n">
+        <v>36587.143</v>
+      </c>
+      <c r="D205" t="n">
+        <v>32837.74</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>3770.283</v>
+      </c>
+      <c r="C206" t="n">
+        <v>36386.914</v>
+      </c>
+      <c r="D206" t="n">
+        <v>32616.631</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>3801.554</v>
+      </c>
+      <c r="C207" t="n">
+        <v>37102.462</v>
+      </c>
+      <c r="D207" t="n">
+        <v>33300.909</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>3841.099</v>
+      </c>
+      <c r="C208" t="n">
+        <v>37237.767</v>
+      </c>
+      <c r="D208" t="n">
+        <v>33396.668</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>3855.017</v>
+      </c>
+      <c r="C209" t="n">
+        <v>38643.413</v>
+      </c>
+      <c r="D209" t="n">
+        <v>34788.396</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2021-05-01</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>3915.181</v>
+      </c>
+      <c r="C210" t="n">
+        <v>39063.452</v>
+      </c>
+      <c r="D210" t="n">
+        <v>35148.272</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>3828.456</v>
+      </c>
+      <c r="C211" t="n">
+        <v>39986.402</v>
+      </c>
+      <c r="D211" t="n">
+        <v>36157.946</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>3800.412</v>
+      </c>
+      <c r="C212" t="n">
+        <v>39649.724</v>
+      </c>
+      <c r="D212" t="n">
+        <v>35849.312</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>3828.949</v>
+      </c>
+      <c r="C213" t="n">
+        <v>39802.171</v>
+      </c>
+      <c r="D213" t="n">
+        <v>35973.223</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>3881.147</v>
+      </c>
+      <c r="C214" t="n">
+        <v>39604.229</v>
+      </c>
+      <c r="D214" t="n">
+        <v>35723.082</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>3837.108</v>
+      </c>
+      <c r="C215" t="n">
+        <v>39801.546</v>
+      </c>
+      <c r="D215" t="n">
+        <v>35964.437</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>3861.557</v>
+      </c>
+      <c r="C216" t="n">
+        <v>40032.107</v>
+      </c>
+      <c r="D216" t="n">
+        <v>36170.55</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>4012.693</v>
+      </c>
+      <c r="C217" t="n">
+        <v>40935.606</v>
+      </c>
+      <c r="D217" t="n">
+        <v>36922.914</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>4004.397</v>
+      </c>
+      <c r="C218" t="n">
+        <v>39947.538</v>
+      </c>
+      <c r="D218" t="n">
+        <v>35943.141</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>4894.232</v>
+      </c>
+      <c r="C219" t="n">
+        <v>44123.519</v>
+      </c>
+      <c r="D219" t="n">
+        <v>39229.287</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>4316.287</v>
+      </c>
+      <c r="C220" t="n">
+        <v>40012.379</v>
+      </c>
+      <c r="D220" t="n">
+        <v>35696.092</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>4395.033</v>
+      </c>
+      <c r="C221" t="n">
+        <v>41293.336</v>
+      </c>
+      <c r="D221" t="n">
+        <v>36898.303</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>4503.791</v>
+      </c>
+      <c r="C222" t="n">
+        <v>41797.074</v>
+      </c>
+      <c r="D222" t="n">
+        <v>37293.283</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>4655.079</v>
+      </c>
+      <c r="C223" t="n">
+        <v>42108.061</v>
+      </c>
+      <c r="D223" t="n">
+        <v>37452.981</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>4466.895</v>
+      </c>
+      <c r="C224" t="n">
+        <v>41310.116</v>
+      </c>
+      <c r="D224" t="n">
+        <v>36843.222</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>4407.627</v>
+      </c>
+      <c r="C225" t="n">
+        <v>40194.69</v>
+      </c>
+      <c r="D225" t="n">
+        <v>35787.064</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>4518.897</v>
+      </c>
+      <c r="C226" t="n">
+        <v>41406.591</v>
+      </c>
+      <c r="D226" t="n">
+        <v>36887.694</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>4557.948</v>
+      </c>
+      <c r="C227" t="n">
+        <v>41769.785</v>
+      </c>
+      <c r="D227" t="n">
+        <v>37211.837</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>4658.657</v>
+      </c>
+      <c r="C228" t="n">
+        <v>41766.33</v>
+      </c>
+      <c r="D228" t="n">
+        <v>37107.673</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>4979.05</v>
+      </c>
+      <c r="C229" t="n">
+        <v>45955.646</v>
+      </c>
+      <c r="D229" t="n">
+        <v>40976.596</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>5116.207</v>
+      </c>
+      <c r="C230" t="n">
+        <v>45398.376</v>
+      </c>
+      <c r="D230" t="n">
+        <v>40282.168</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>5174.94</v>
+      </c>
+      <c r="C231" t="n">
+        <v>45189.528</v>
+      </c>
+      <c r="D231" t="n">
+        <v>40014.588</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>5028.693</v>
+      </c>
+      <c r="C232" t="n">
+        <v>46402.517</v>
+      </c>
+      <c r="D232" t="n">
+        <v>41373.824</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>5179.834</v>
+      </c>
+      <c r="C233" t="n">
+        <v>46173.887</v>
+      </c>
+      <c r="D233" t="n">
+        <v>40994.054</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>5123.128</v>
+      </c>
+      <c r="C234" t="n">
+        <v>46713.994</v>
+      </c>
+      <c r="D234" t="n">
+        <v>41590.866</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>5527.787</v>
+      </c>
+      <c r="C235" t="n">
+        <v>47997.948</v>
+      </c>
+      <c r="D235" t="n">
+        <v>42470.161</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>5615.323</v>
+      </c>
+      <c r="C236" t="n">
+        <v>48001.574</v>
+      </c>
+      <c r="D236" t="n">
+        <v>42386.251</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>5666.138</v>
+      </c>
+      <c r="C237" t="n">
+        <v>48911.183</v>
+      </c>
+      <c r="D237" t="n">
+        <v>43245.045</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>5804.336</v>
+      </c>
+      <c r="C238" t="n">
+        <v>49551.861</v>
+      </c>
+      <c r="D238" t="n">
+        <v>43747.525</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>5878.159</v>
+      </c>
+      <c r="C239" t="n">
+        <v>49877.147</v>
+      </c>
+      <c r="D239" t="n">
+        <v>43998.988</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>5992.43</v>
+      </c>
+      <c r="C240" t="n">
+        <v>52290.293</v>
+      </c>
+      <c r="D240" t="n">
+        <v>46297.863</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>6182.314</v>
+      </c>
+      <c r="C241" t="n">
+        <v>57069.692</v>
+      </c>
+      <c r="D241" t="n">
+        <v>50887.379</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>6305.457</v>
+      </c>
+      <c r="C242" t="n">
+        <v>54201.928</v>
+      </c>
+      <c r="D242" t="n">
+        <v>47896.471</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>6362.987</v>
+      </c>
+      <c r="C243" t="n">
+        <v>54295.895</v>
+      </c>
+      <c r="D243" t="n">
+        <v>47932.908</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>6466.591</v>
+      </c>
+      <c r="C244" t="n">
+        <v>54981.789</v>
+      </c>
+      <c r="D244" t="n">
+        <v>48515.198</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>6105.65</v>
+      </c>
+      <c r="C245" t="n">
+        <v>55008.464</v>
+      </c>
+      <c r="D245" t="n">
+        <v>48902.813</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>6380.708</v>
+      </c>
+      <c r="C246" t="n">
+        <v>57565.936</v>
+      </c>
+      <c r="D246" t="n">
+        <v>51185.228</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>6523.462</v>
+      </c>
+      <c r="C247" t="n">
+        <v>62184.86</v>
+      </c>
+      <c r="D247" t="n">
+        <v>55661.398</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>6651.499</v>
+      </c>
+      <c r="C248" t="n">
+        <v>61135.613</v>
+      </c>
+      <c r="D248" t="n">
+        <v>54484.114</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>6869.286</v>
+      </c>
+      <c r="C249" t="n">
+        <v>61433.45</v>
+      </c>
+      <c r="D249" t="n">
+        <v>54564.164</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>6958.808</v>
+      </c>
+      <c r="C250" t="n">
+        <v>62687.276</v>
+      </c>
+      <c r="D250" t="n">
+        <v>55728.468</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>7017.597</v>
+      </c>
+      <c r="C251" t="n">
+        <v>62889.773</v>
+      </c>
+      <c r="D251" t="n">
+        <v>55872.176</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>7096.943</v>
+      </c>
+      <c r="C252" t="n">
+        <v>62490.329</v>
+      </c>
+      <c r="D252" t="n">
+        <v>55393.386</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>7338.884</v>
+      </c>
+      <c r="C253" t="n">
+        <v>71238.14599999999</v>
+      </c>
+      <c r="D253" t="n">
+        <v>63899.262</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>7459.942</v>
+      </c>
+      <c r="C254" t="n">
+        <v>65895.936</v>
+      </c>
+      <c r="D254" t="n">
+        <v>58435.994</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>7577.497</v>
+      </c>
+      <c r="C255" t="n">
+        <v>66241.99800000001</v>
+      </c>
+      <c r="D255" t="n">
+        <v>58664.501</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>7742.584</v>
+      </c>
+      <c r="C256" t="n">
+        <v>69989.442</v>
+      </c>
+      <c r="D256" t="n">
+        <v>62246.857</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>7397.183</v>
+      </c>
+      <c r="C257" t="n">
+        <v>67244.459</v>
+      </c>
+      <c r="D257" t="n">
+        <v>59847.277</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>7482.474</v>
+      </c>
+      <c r="C258" t="n">
+        <v>68207.173</v>
+      </c>
+      <c r="D258" t="n">
+        <v>60724.699</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>7605.455</v>
+      </c>
+      <c r="C259" t="n">
+        <v>72599.60799999999</v>
+      </c>
+      <c r="D259" t="n">
+        <v>64994.154</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>7709.801</v>
+      </c>
+      <c r="C260" t="n">
+        <v>70133.414</v>
+      </c>
+      <c r="D260" t="n">
+        <v>62423.613</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>7797.854</v>
+      </c>
+      <c r="C261" t="n">
+        <v>72123.542</v>
+      </c>
+      <c r="D261" t="n">
+        <v>64325.688</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>7957.531</v>
+      </c>
+      <c r="C262" t="n">
+        <v>75584.329</v>
+      </c>
+      <c r="D262" t="n">
+        <v>67626.799</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>8022.612</v>
+      </c>
+      <c r="C263" t="n">
+        <v>73718.637</v>
+      </c>
+      <c r="D263" t="n">
+        <v>65696.02499999999</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>8127.354</v>
+      </c>
+      <c r="C264" t="n">
+        <v>74392.734</v>
+      </c>
+      <c r="D264" t="n">
+        <v>66265.379</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>8455.129999999999</v>
+      </c>
+      <c r="C265" t="n">
+        <v>85425.63800000001</v>
+      </c>
+      <c r="D265" t="n">
+        <v>76970.50900000001</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>8533.648999999999</v>
+      </c>
+      <c r="C266" t="n">
+        <v>78700.696</v>
+      </c>
+      <c r="D266" t="n">
+        <v>70167.04700000001</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>8612.335999999999</v>
+      </c>
+      <c r="C267" t="n">
+        <v>80068.13499999999</v>
+      </c>
+      <c r="D267" t="n">
+        <v>71455.8</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>8352.298000000001</v>
+      </c>
+      <c r="C268" t="n">
+        <v>85039.788</v>
+      </c>
+      <c r="D268" t="n">
+        <v>76687.49000000001</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>8299.457</v>
+      </c>
+      <c r="C269" t="n">
+        <v>84174.837</v>
+      </c>
+      <c r="D269" t="n">
+        <v>75875.38</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>8415.074000000001</v>
+      </c>
+      <c r="C270" t="n">
+        <v>86616.011</v>
+      </c>
+      <c r="D270" t="n">
+        <v>78200.93700000001</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>8641.749</v>
+      </c>
+      <c r="C271" t="n">
+        <v>92008.677</v>
+      </c>
+      <c r="D271" t="n">
+        <v>83366.928</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>8776.029</v>
+      </c>
+      <c r="C272" t="n">
+        <v>88314.736</v>
+      </c>
+      <c r="D272" t="n">
+        <v>79538.70699999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D272"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>огноо</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Нийт хөрөнгө</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Нийт өр төлбөр</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Өөрийн хөрөнгө</t>
         </is>
       </c>
     </row>

--- a/data.mn/public/datasets/mongolbank-bank-balance-sheet.xlsx
+++ b/data.mn/public/datasets/mongolbank-bank-balance-sheet.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D272"/>
+  <dimension ref="A1:D274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4779,6 +4779,38 @@
       </c>
       <c r="D272" t="n">
         <v>79538.70699999999</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>8967.593000000001</v>
+      </c>
+      <c r="C273" t="n">
+        <v>90620.315</v>
+      </c>
+      <c r="D273" t="n">
+        <v>81652.723</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>9138.621999999999</v>
+      </c>
+      <c r="C274" t="n">
+        <v>94937.473</v>
+      </c>
+      <c r="D274" t="n">
+        <v>85798.851</v>
       </c>
     </row>
   </sheetData>
@@ -4792,7 +4824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D272"/>
+  <dimension ref="A1:D274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9159,6 +9191,38 @@
         <v>8776.029</v>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>90620.315</v>
+      </c>
+      <c r="C273" t="n">
+        <v>81652.723</v>
+      </c>
+      <c r="D273" t="n">
+        <v>8967.593000000001</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>94937.473</v>
+      </c>
+      <c r="C274" t="n">
+        <v>85798.851</v>
+      </c>
+      <c r="D274" t="n">
+        <v>9138.621999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
